--- a/SCENARIOS/SCENARIO 3/Simulation Results/DStarLite_SCENARIO_3_Benchmarking_5_APM_DF.xlsx
+++ b/SCENARIOS/SCENARIO 3/Simulation Results/DStarLite_SCENARIO_3_Benchmarking_5_APM_DF.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10513"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felipenoris/tmp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gavin\Documents\GitHub\evac\SCENARIOS\SCENARIO 3\Simulation Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C353BCB8-5EC8-0143-BDD3-A1B661DAACD7}" xr6:coauthVersionLast="33" xr6:coauthVersionMax="33" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA022B34-3938-432A-8000-00DE5F6B3137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="460" windowWidth="28040" windowHeight="17040" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Run</t>
   </si>
@@ -33,7 +44,10 @@
     <t>Seed</t>
   </si>
   <si>
-    <t>PathfindingTime_s</t>
+    <t>InitialPathfindingTime_s</t>
+  </si>
+  <si>
+    <t>IncrementalPathfindingTime_s</t>
   </si>
   <si>
     <t>SimulationTime_s</t>
@@ -45,7 +59,13 @@
     <t>Number of runs</t>
   </si>
   <si>
-    <t>Average pathfinding time (s)</t>
+    <t>Average initial pathfinding time (s)</t>
+  </si>
+  <si>
+    <t>Average incremental pathfinding time (s)</t>
+  </si>
+  <si>
+    <t>Average total pathfinding time (s)</t>
   </si>
   <si>
     <t>Average simulation time (s)</t>
@@ -88,7 +108,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -104,9 +124,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Θέμα Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -144,7 +164,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -250,7 +270,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -392,7 +412,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -400,10 +420,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:E54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F66"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.69921875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -419,879 +442,1069 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>4.155892324e9</v>
+        <v>1228606532</v>
       </c>
       <c r="C2">
-        <v>472.8377819</v>
+        <v>44.369603699999999</v>
       </c>
       <c r="D2">
-        <v>1.4590628999999982</v>
+        <v>518.64005450000002</v>
       </c>
       <c r="E2">
-        <v>6.685000000000005</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>1.4115101999999973</v>
+      </c>
+      <c r="F2">
+        <v>2.120000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>3.906331185e9</v>
+        <v>1343860626</v>
       </c>
       <c r="C3">
-        <v>461.11080960000004</v>
+        <v>73.644086400000006</v>
       </c>
       <c r="D3">
-        <v>0.006674300000000002</v>
+        <v>609.14412879999998</v>
       </c>
       <c r="E3">
-        <v>3.750000000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>9.4810000000000068E-3</v>
+      </c>
+      <c r="F3">
+        <v>3.1800000000000019</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>3.25551176e8</v>
+        <v>3692796533</v>
       </c>
       <c r="C4">
-        <v>405.7066942999999</v>
+        <v>52.8790142</v>
       </c>
       <c r="D4">
-        <v>0.006188800000000002</v>
+        <v>617.80425390000005</v>
       </c>
       <c r="E4">
-        <v>3.050000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>7.5987999999999924E-3</v>
+      </c>
+      <c r="F4">
+        <v>3.1700000000000021</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>9.94779052e8</v>
+        <v>2194341356</v>
       </c>
       <c r="C5">
-        <v>392.96852729999995</v>
+        <v>52.629071799999998</v>
       </c>
       <c r="D5">
-        <v>0.007651999999999999</v>
+        <v>544.81179520000001</v>
       </c>
       <c r="E5">
-        <v>6.070000000000005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>7.2854E-3</v>
+      </c>
+      <c r="F5">
+        <v>3.7900000000000023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>1.383084542e9</v>
+        <v>1421713398</v>
       </c>
       <c r="C6">
-        <v>393.5232786</v>
+        <v>53.309055899999997</v>
       </c>
       <c r="D6">
-        <v>0.006358999999999996</v>
+        <v>558.43398300000001</v>
       </c>
       <c r="E6">
-        <v>3.525000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>7.6070999999999925E-3</v>
+      </c>
+      <c r="F6">
+        <v>4.3650000000000029</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>1.336730255e9</v>
+        <v>152156325</v>
       </c>
       <c r="C7">
-        <v>395.50690649999996</v>
+        <v>48.275274699999997</v>
       </c>
       <c r="D7">
-        <v>0.012779399999999948</v>
+        <v>532.4501947</v>
       </c>
       <c r="E7">
-        <v>3.145000000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>7.7381000000000004E-3</v>
+      </c>
+      <c r="F7">
+        <v>1.9500000000000013</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>7.68271729e8</v>
+        <v>1829766091</v>
       </c>
       <c r="C8">
-        <v>449.3039858</v>
+        <v>53.103056299999999</v>
       </c>
       <c r="D8">
-        <v>0.0067122999999999974</v>
+        <v>499.91519099999999</v>
       </c>
       <c r="E8">
-        <v>4.935000000000004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>7.6678999999999975E-3</v>
+      </c>
+      <c r="F8">
+        <v>3.5600000000000023</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>3.920859163e9</v>
+        <v>1739421019</v>
       </c>
       <c r="C9">
-        <v>463.35002440000005</v>
+        <v>42.878678000000001</v>
       </c>
       <c r="D9">
-        <v>0.007033700000000003</v>
+        <v>481.49017469999995</v>
       </c>
       <c r="E9">
-        <v>4.605000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>1.4082999999999972E-2</v>
+      </c>
+      <c r="F9">
+        <v>2.5500000000000016</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>1.959566253e9</v>
+        <v>608956404</v>
       </c>
       <c r="C10">
-        <v>450.73299130000004</v>
+        <v>42.162312799999995</v>
       </c>
       <c r="D10">
-        <v>0.006314000000000001</v>
+        <v>482.44261100000006</v>
       </c>
       <c r="E10">
-        <v>3.1700000000000017</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>6.4997000000000067E-3</v>
+      </c>
+      <c r="F10">
+        <v>3.4400000000000022</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>4.093302042e9</v>
+        <v>1250392422</v>
       </c>
       <c r="C11">
-        <v>407.65181060000003</v>
+        <v>42.742898700000005</v>
       </c>
       <c r="D11">
-        <v>0.006280600000000006</v>
+        <v>480.54160149999996</v>
       </c>
       <c r="E11">
-        <v>4.255000000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>7.3839999999999991E-3</v>
+      </c>
+      <c r="F11">
+        <v>4.5650000000000031</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>1.617328393e9</v>
+        <v>4108474249</v>
       </c>
       <c r="C12">
-        <v>393.35537370000003</v>
+        <v>43.5121422</v>
       </c>
       <c r="D12">
-        <v>0.005981500000000015</v>
+        <v>481.45512770000005</v>
       </c>
       <c r="E12">
-        <v>3.6700000000000026</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>6.5552999999999939E-3</v>
+      </c>
+      <c r="F12">
+        <v>3.635000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>1.873025139e9</v>
+        <v>3359570532</v>
       </c>
       <c r="C13">
-        <v>396.3806895</v>
+        <v>41.894772400000001</v>
       </c>
       <c r="D13">
-        <v>0.006211900000000005</v>
+        <v>476.50520080000001</v>
       </c>
       <c r="E13">
-        <v>4.190000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>6.5667999999999907E-3</v>
+      </c>
+      <c r="F13">
+        <v>4.5200000000000031</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>3.580749509e9</v>
+        <v>300700514</v>
       </c>
       <c r="C14">
-        <v>396.9672526</v>
+        <v>42.623182100000001</v>
       </c>
       <c r="D14">
-        <v>0.006051199999999999</v>
+        <v>482.0361997</v>
       </c>
       <c r="E14">
-        <v>4.570000000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>6.5062999999999926E-3</v>
+      </c>
+      <c r="F14">
+        <v>3.8450000000000024</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>6.35752566e8</v>
+        <v>3762584573</v>
       </c>
       <c r="C15">
-        <v>398.68481710000003</v>
+        <v>43.336325200000005</v>
       </c>
       <c r="D15">
-        <v>0.0065866000000000015</v>
+        <v>2595.6476808000002</v>
       </c>
       <c r="E15">
-        <v>1.935000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>7.2981000000000061E-3</v>
+      </c>
+      <c r="F15">
+        <v>4.2700000000000031</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>1.350711278e9</v>
+        <v>1282959334</v>
       </c>
       <c r="C16">
-        <v>462.25293189999996</v>
+        <v>40.627752100000002</v>
       </c>
       <c r="D16">
-        <v>0.00788250000000001</v>
+        <v>466.29083889999993</v>
       </c>
       <c r="E16">
-        <v>4.480000000000003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>6.0200000000000019E-3</v>
+      </c>
+      <c r="F16">
+        <v>4.2650000000000032</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>9.34238568e8</v>
+        <v>1687637171</v>
       </c>
       <c r="C17">
-        <v>520.8066773</v>
+        <v>41.7272733</v>
       </c>
       <c r="D17">
-        <v>0.008589900000000003</v>
+        <v>464.67702519999995</v>
       </c>
       <c r="E17">
-        <v>4.705000000000003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>6.1751999999999935E-3</v>
+      </c>
+      <c r="F17">
+        <v>4.610000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>3.245628379e9</v>
+        <v>3365977044</v>
       </c>
       <c r="C18">
-        <v>473.6358534</v>
+        <v>41.994606300000001</v>
       </c>
       <c r="D18">
-        <v>0.006598499999999996</v>
+        <v>467.77219070000001</v>
       </c>
       <c r="E18">
-        <v>1.830000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>6.302900000000001E-3</v>
+      </c>
+      <c r="F18">
+        <v>4.3850000000000033</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>1.570734046e9</v>
+        <v>3789806038</v>
       </c>
       <c r="C19">
-        <v>658.6787099000001</v>
+        <v>40.750194300000004</v>
       </c>
       <c r="D19">
-        <v>0.009239699999999983</v>
+        <v>465.6704052</v>
       </c>
       <c r="E19">
-        <v>4.270000000000003</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>1.3826800000000016E-2</v>
+      </c>
+      <c r="F19">
+        <v>5.7650000000000041</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>1.912136029e9</v>
+        <v>2963929775</v>
       </c>
       <c r="C20">
-        <v>669.4625744</v>
+        <v>41.650496699999998</v>
       </c>
       <c r="D20">
-        <v>0.01052029999999998</v>
+        <v>465.9268682</v>
       </c>
       <c r="E20">
-        <v>1.790000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>6.0734999999999973E-3</v>
+      </c>
+      <c r="F20">
+        <v>4.5700000000000029</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>3.688318757e9</v>
+        <v>942674459</v>
       </c>
       <c r="C21">
-        <v>553.7781665</v>
+        <v>41.747637000000005</v>
       </c>
       <c r="D21">
-        <v>0.008691799999999996</v>
+        <v>466.03551779999998</v>
       </c>
       <c r="E21">
-        <v>5.575000000000004</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>6.0613999999999937E-3</v>
+      </c>
+      <c r="F21">
+        <v>2.7100000000000017</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>2.423786927e9</v>
+        <v>1614320739</v>
       </c>
       <c r="C22">
-        <v>474.5218468</v>
+        <v>40.482663799999997</v>
       </c>
       <c r="D22">
-        <v>0.0063949000000000054</v>
+        <v>977.74330929999996</v>
       </c>
       <c r="E22">
-        <v>3.695000000000002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>9.3309000000000083E-3</v>
+      </c>
+      <c r="F22">
+        <v>4.2850000000000028</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>1.837231154e9</v>
+        <v>732791547</v>
       </c>
       <c r="C23">
-        <v>617.9071715</v>
+        <v>55.454143299999998</v>
       </c>
       <c r="D23">
-        <v>0.008339500000000001</v>
+        <v>526.749416</v>
       </c>
       <c r="E23">
-        <v>2.080000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>8.8772000000000087E-3</v>
+      </c>
+      <c r="F23">
+        <v>3.6850000000000023</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>1.866929802e9</v>
+        <v>3471663516</v>
       </c>
       <c r="C24">
-        <v>578.0079833</v>
+        <v>43.120923900000001</v>
       </c>
       <c r="D24">
-        <v>0.008015000000000003</v>
+        <v>500.28626450000002</v>
       </c>
       <c r="E24">
-        <v>6.0400000000000045</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>8.6980000000000026E-3</v>
+      </c>
+      <c r="F24">
+        <v>3.6650000000000023</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>9.74783072e8</v>
+        <v>58305159</v>
       </c>
       <c r="C25">
-        <v>453.2596886</v>
+        <v>41.1312967</v>
       </c>
       <c r="D25">
-        <v>0.008842000000000001</v>
+        <v>467.46813759999998</v>
       </c>
       <c r="E25">
-        <v>5.065000000000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>6.9506000000000038E-3</v>
+      </c>
+      <c r="F25">
+        <v>4.8550000000000031</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>1.029381164e9</v>
+        <v>2763116958</v>
       </c>
       <c r="C26">
-        <v>495.5839559</v>
+        <v>50.3639796</v>
       </c>
       <c r="D26">
-        <v>0.008489200000000004</v>
+        <v>481.69449409999999</v>
       </c>
       <c r="E26">
-        <v>3.8000000000000025</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>7.5121999999999915E-3</v>
+      </c>
+      <c r="F26">
+        <v>4.4150000000000027</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>2.720724348e9</v>
+        <v>888246742</v>
       </c>
       <c r="C27">
-        <v>524.6747191</v>
+        <v>43.393289799999998</v>
       </c>
       <c r="D27">
-        <v>0.008642099999999995</v>
+        <v>487.03087469999997</v>
       </c>
       <c r="E27">
-        <v>3.6600000000000024</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>6.5719999999999997E-3</v>
+      </c>
+      <c r="F27">
+        <v>4.0550000000000033</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="B28">
-        <v>3.995443749e9</v>
+        <v>1021950696</v>
       </c>
       <c r="C28">
-        <v>439.912374</v>
+        <v>42.475608000000001</v>
       </c>
       <c r="D28">
-        <v>0.006657200000000007</v>
+        <v>485.45575009999999</v>
       </c>
       <c r="E28">
-        <v>2.8150000000000017</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>6.7887000000000077E-3</v>
+      </c>
+      <c r="F28">
+        <v>3.1100000000000021</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="B29">
-        <v>2.95464684e8</v>
+        <v>2337825898</v>
       </c>
       <c r="C29">
-        <v>439.7473799000001</v>
+        <v>50.111282200000005</v>
       </c>
       <c r="D29">
-        <v>0.007298399999999991</v>
+        <v>486.18916359999992</v>
       </c>
       <c r="E29">
-        <v>4.870000000000003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>6.1237999999999952E-3</v>
+      </c>
+      <c r="F29">
+        <v>3.3700000000000023</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="B30">
-        <v>4.117644043e9</v>
+        <v>624090600</v>
       </c>
       <c r="C30">
-        <v>438.1633869</v>
+        <v>43.110964499999994</v>
       </c>
       <c r="D30">
-        <v>0.007392999999999995</v>
+        <v>484.8801486000001</v>
       </c>
       <c r="E30">
-        <v>2.435000000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>6.4642000000000015E-3</v>
+      </c>
+      <c r="F30">
+        <v>2.9800000000000018</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="B31">
-        <v>2.89144371e9</v>
+        <v>2695822453</v>
       </c>
       <c r="C31">
-        <v>441.7195538000001</v>
+        <v>42.696099700000005</v>
       </c>
       <c r="D31">
-        <v>0.007387299999999997</v>
+        <v>481.00002310000002</v>
       </c>
       <c r="E31">
-        <v>3.4200000000000026</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>6.1750000000000025E-3</v>
+      </c>
+      <c r="F31">
+        <v>5.6650000000000036</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>3.766973561e9</v>
+        <v>3894053922</v>
       </c>
       <c r="C32">
-        <v>439.1689718</v>
+        <v>45.880409299999997</v>
       </c>
       <c r="D32">
-        <v>0.006984099999999993</v>
+        <v>484.07261489999996</v>
       </c>
       <c r="E32">
-        <v>3.3950000000000022</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>6.6587000000000009E-3</v>
+      </c>
+      <c r="F32">
+        <v>3.8550000000000022</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>4.103854938e9</v>
+        <v>2905419385</v>
       </c>
       <c r="C33">
-        <v>436.83150489999997</v>
+        <v>43.629621999999998</v>
       </c>
       <c r="D33">
-        <v>0.0066854999999999875</v>
+        <v>3346.9341697</v>
       </c>
       <c r="E33">
-        <v>4.730000000000003</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>6.4270000000000022E-3</v>
+      </c>
+      <c r="F33">
+        <v>1.9350000000000009</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="B34">
-        <v>2.038226596e9</v>
+        <v>3083102081</v>
       </c>
       <c r="C34">
-        <v>438.1087535000001</v>
+        <v>39.699921000000003</v>
       </c>
       <c r="D34">
-        <v>0.006408199999999999</v>
+        <v>456.72306240000006</v>
       </c>
       <c r="E34">
-        <v>3.1500000000000017</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>6.2791999999999926E-3</v>
+      </c>
+      <c r="F34">
+        <v>5.6200000000000045</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>1.886877205e9</v>
+        <v>159462890</v>
       </c>
       <c r="C35">
-        <v>439.73928499999994</v>
+        <v>40.783706000000002</v>
       </c>
       <c r="D35">
-        <v>0.007469100000000006</v>
+        <v>457.18765500000001</v>
       </c>
       <c r="E35">
-        <v>4.015000000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>6.0717999999999918E-3</v>
+      </c>
+      <c r="F35">
+        <v>3.9000000000000021</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>3.842817204e9</v>
+        <v>3990132296</v>
       </c>
       <c r="C36">
-        <v>441.801984</v>
+        <v>41.186047500000001</v>
       </c>
       <c r="D36">
-        <v>0.0068397000000000084</v>
+        <v>458.22777860000002</v>
       </c>
       <c r="E36">
-        <v>5.055000000000003</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>5.8929000000000091E-3</v>
+      </c>
+      <c r="F36">
+        <v>2.2750000000000012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>4.86354069e8</v>
+        <v>2435457443</v>
       </c>
       <c r="C37">
-        <v>438.2144003</v>
+        <v>40.681545399999997</v>
       </c>
       <c r="D37">
-        <v>0.006679599999999994</v>
+        <v>455.43276219999996</v>
       </c>
       <c r="E37">
-        <v>4.950000000000004</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>6.9815999999999906E-3</v>
+      </c>
+      <c r="F37">
+        <v>4.6850000000000032</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>1.264526896e9</v>
+        <v>1580063518</v>
       </c>
       <c r="C38">
-        <v>437.34036690000005</v>
+        <v>40.848581200000005</v>
       </c>
       <c r="D38">
-        <v>0.006767700000000007</v>
+        <v>459.49865399999999</v>
       </c>
       <c r="E38">
-        <v>2.6200000000000014</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>6.3572999999999867E-3</v>
+      </c>
+      <c r="F38">
+        <v>3.8600000000000025</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>2.361368128e9</v>
+        <v>3481136979</v>
       </c>
       <c r="C39">
-        <v>437.19217610000004</v>
+        <v>41.135321499999996</v>
       </c>
       <c r="D39">
-        <v>0.007434599999999999</v>
+        <v>460.3286784</v>
       </c>
       <c r="E39">
-        <v>2.4050000000000016</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>6.5809999999999879E-3</v>
+      </c>
+      <c r="F39">
+        <v>3.4150000000000023</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>3.724747118e9</v>
+        <v>1109325860</v>
       </c>
       <c r="C40">
-        <v>438.6553650000001</v>
+        <v>39.990018999999997</v>
       </c>
       <c r="D40">
-        <v>0.006392599999999994</v>
+        <v>2410.9155157</v>
       </c>
       <c r="E40">
-        <v>1.980000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>7.5066999999999903E-3</v>
+      </c>
+      <c r="F40">
+        <v>2.0600000000000014</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="B41">
-        <v>1.469988676e9</v>
+        <v>2720121753</v>
       </c>
       <c r="C41">
-        <v>438.7000329999999</v>
+        <v>42.183220399999996</v>
       </c>
       <c r="D41">
-        <v>0.00748300000000001</v>
+        <v>479.02960349999995</v>
       </c>
       <c r="E41">
-        <v>3.135000000000002</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>6.4475999999999952E-3</v>
+      </c>
+      <c r="F41">
+        <v>3.8750000000000022</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="B42">
-        <v>4.85722684e8</v>
+        <v>1201216430</v>
       </c>
       <c r="C42">
-        <v>436.29603439999994</v>
+        <v>41.296297599999995</v>
       </c>
       <c r="D42">
-        <v>0.0072842</v>
+        <v>460.98897529999999</v>
       </c>
       <c r="E42">
-        <v>5.360000000000004</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>6.4212999999999926E-3</v>
+      </c>
+      <c r="F42">
+        <v>4.7000000000000037</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="B43">
-        <v>2.832445013e9</v>
+        <v>3707347077</v>
       </c>
       <c r="C43">
-        <v>435.57158419999996</v>
+        <v>40.268562299999999</v>
       </c>
       <c r="D43">
-        <v>0.006790899999999986</v>
+        <v>460.61239890000002</v>
       </c>
       <c r="E43">
-        <v>4.305000000000002</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>1.5105900000000011E-2</v>
+      </c>
+      <c r="F43">
+        <v>3.240000000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="B44">
-        <v>3.424033792e9</v>
+        <v>3195933215</v>
       </c>
       <c r="C44">
-        <v>440.6599294</v>
+        <v>40.797320399999997</v>
       </c>
       <c r="D44">
-        <v>0.007139100000000001</v>
+        <v>459.15760050000006</v>
       </c>
       <c r="E44">
-        <v>3.4750000000000023</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>6.2583999999999921E-3</v>
+      </c>
+      <c r="F44">
+        <v>2.1650000000000014</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="B45">
-        <v>3.802873252e9</v>
+        <v>200700799</v>
       </c>
       <c r="C45">
-        <v>438.1969833</v>
+        <v>42.875406499999997</v>
       </c>
       <c r="D45">
-        <v>0.006596700000000005</v>
+        <v>459.17474330000005</v>
       </c>
       <c r="E45">
-        <v>5.475000000000005</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>6.2053999999999929E-3</v>
+      </c>
+      <c r="F45">
+        <v>4.1500000000000021</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="B46">
-        <v>3.117601195e9</v>
+        <v>2950022149</v>
       </c>
       <c r="C46">
-        <v>443.36408760000006</v>
+        <v>40.2653842</v>
       </c>
       <c r="D46">
-        <v>0.006810600000000007</v>
+        <v>458.74410050000006</v>
       </c>
       <c r="E46">
-        <v>2.5950000000000015</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>6.2291999999999998E-3</v>
+      </c>
+      <c r="F46">
+        <v>4.8500000000000032</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="B47">
-        <v>3.8867164e8</v>
+        <v>1359917078</v>
       </c>
       <c r="C47">
-        <v>438.2176257</v>
+        <v>41.258458699999998</v>
       </c>
       <c r="D47">
-        <v>0.007358600000000002</v>
+        <v>463.90189830000003</v>
       </c>
       <c r="E47">
-        <v>4.925000000000003</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48">
-        <v>47.0</v>
+        <v>7.1505999999999965E-3</v>
+      </c>
+      <c r="F47">
+        <v>4.6450000000000031</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>6</v>
       </c>
       <c r="B48">
-        <v>3.116849488e9</v>
-      </c>
-      <c r="C48">
-        <v>436.81129289999996</v>
-      </c>
-      <c r="D48">
-        <v>0.0068014999999999985</v>
-      </c>
-      <c r="E48">
-        <v>2.8400000000000016</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49">
-        <v>48.0</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>7</v>
       </c>
       <c r="B49">
-        <v>4.77082229e8</v>
-      </c>
-      <c r="C49">
-        <v>437.4361911</v>
-      </c>
-      <c r="D49">
-        <v>0.006271300000000006</v>
-      </c>
-      <c r="E49">
-        <v>4.200000000000003</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50">
-        <v>49.0</v>
+        <v>44.369076273913024</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>8</v>
       </c>
       <c r="B50">
-        <v>4.92643662e8</v>
-      </c>
-      <c r="C50">
-        <v>438.69021520000007</v>
-      </c>
-      <c r="D50">
-        <v>0.007743900000000012</v>
-      </c>
-      <c r="E50">
-        <v>5.150000000000003</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51">
-        <v>50.0</v>
+        <v>647.11127904565217</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>9</v>
       </c>
       <c r="B51">
-        <v>3.683218103e9</v>
-      </c>
-      <c r="C51">
-        <v>437.5859032</v>
-      </c>
-      <c r="D51">
-        <v>0.007615500000000001</v>
-      </c>
-      <c r="E51">
-        <v>5.2500000000000036</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <f>B49+B50</f>
+        <v>691.48035531956521</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B52">
+        <v>3.7919754347826025E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>47</v>
+      </c>
+      <c r="B62">
+        <v>2427461744</v>
+      </c>
+      <c r="C62">
+        <v>41.457747500000004</v>
+      </c>
+      <c r="D62">
+        <v>60912.979255800004</v>
+      </c>
+      <c r="E62">
+        <v>3.4448899999999991E-2</v>
+      </c>
+      <c r="F62">
+        <v>3.0200000000000014</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>48</v>
+      </c>
+      <c r="B63">
+        <v>3607381351</v>
+      </c>
+      <c r="C63">
+        <v>79.854843500000001</v>
+      </c>
+      <c r="D63">
+        <v>864.13188400000001</v>
+      </c>
+      <c r="E63">
+        <v>0.20984680000000006</v>
+      </c>
+      <c r="F63">
+        <v>3.3700000000000019</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>49</v>
+      </c>
+      <c r="B64">
+        <v>3019864208</v>
+      </c>
+      <c r="C64">
+        <v>81.782299899999998</v>
+      </c>
+      <c r="D64">
+        <v>848.77198509999994</v>
+      </c>
+      <c r="E64">
+        <v>9.8992700000000086E-2</v>
+      </c>
+      <c r="F64">
+        <v>5.3000000000000034</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65">
         <v>50</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" t="s">
-        <v>6</v>
-      </c>
-      <c r="B53">
-        <v>457.77553207799997</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54">
-        <v>0.03636851799999997</v>
+      <c r="B65">
+        <v>2569715770</v>
+      </c>
+      <c r="C65">
+        <v>79.918005399999998</v>
+      </c>
+      <c r="D65">
+        <v>760.89591650000011</v>
+      </c>
+      <c r="E65">
+        <v>1.8009400000000012E-2</v>
+      </c>
+      <c r="F65">
+        <v>3.2350000000000021</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>51</v>
+      </c>
+      <c r="B66">
+        <v>410607902</v>
+      </c>
+      <c r="C66">
+        <v>47.148687799999998</v>
+      </c>
+      <c r="D66">
+        <v>1040.2579061000001</v>
+      </c>
+      <c r="E66">
+        <v>2.590399999999999E-2</v>
+      </c>
+      <c r="F66">
+        <v>5.9950000000000045</v>
       </c>
     </row>
   </sheetData>
